--- a/data/trans_orig/IP16B06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B06-Estudios-trans_orig.xlsx
@@ -2405,7 +2405,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
